--- a/donhang_test/import_template.xlsx
+++ b/donhang_test/import_template.xlsx
@@ -1,41 +1,131 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DO_AN\PetMatching\donhang_test\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C4BDCFF-BBEB-4808-92E8-13CC37522593}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Sản phẩm nhập" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="33">
+  <si>
+    <t>Mã sản phẩm</t>
+  </si>
+  <si>
+    <t>Tên sản phẩm</t>
+  </si>
+  <si>
+    <t>Phân loại</t>
+  </si>
+  <si>
+    <t>Danh mục</t>
+  </si>
+  <si>
+    <t>Thương hiệu</t>
+  </si>
+  <si>
+    <t>Đơn vị tính</t>
+  </si>
+  <si>
+    <t>Giá nhập</t>
+  </si>
+  <si>
+    <t>Giá bán</t>
+  </si>
+  <si>
+    <t>Giá khuyến mãi</t>
+  </si>
+  <si>
+    <t>Số lượng nhập</t>
+  </si>
+  <si>
+    <t>Loài mục tiêu</t>
+  </si>
+  <si>
+    <t>Thông số kỹ thuật</t>
+  </si>
+  <si>
+    <t>Mô tả</t>
+  </si>
+  <si>
+    <t>128222</t>
+  </si>
+  <si>
+    <t>Luoc chai long tu dong cho thu cung</t>
+  </si>
+  <si>
+    <t>Size M</t>
+  </si>
+  <si>
+    <t>GROOMING</t>
+  </si>
+  <si>
+    <t>FurCare</t>
+  </si>
+  <si>
+    <t>cái</t>
+  </si>
+  <si>
+    <t>ALL</t>
+  </si>
+  <si>
+    <t>Màu sắc: Hồng, Kích thước: Trung bình, Chất liệu: Nhựa &amp; Thép</t>
+  </si>
+  <si>
+    <t>Lược chải lông tự động cho chó mèo.</t>
+  </si>
+  <si>
+    <t>Size S</t>
+  </si>
+  <si>
+    <t>Màu sắc: Xanh, Kích thước: Nhỏ, Chất liệu: Nhựa &amp; Thép</t>
+  </si>
+  <si>
+    <t>999999</t>
+  </si>
+  <si>
+    <t>Sản phẩm thử nghiệm mới Excel</t>
+  </si>
+  <si>
+    <t>Hộp 500g</t>
+  </si>
+  <si>
+    <t>ACCESSORY</t>
+  </si>
+  <si>
+    <t>PetBrand</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>CAT</t>
+  </si>
+  <si>
+    <t>Chất liệu: Cotton, Độ bền: Cao</t>
+  </si>
+  <si>
+    <t>Sản phẩm test tạo mới hoàn toàn từ file Excel.</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -65,13 +155,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -396,126 +494,182 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:M4"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="11" max="11" width="13.33203125" customWidth="1"/>
+    <col min="12" max="12" width="52.33203125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Mã sản phẩm</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Tên sản phẩm</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Danh mục</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Thương hiệu</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Đơn vị tính</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Giá nhập</v>
-      </c>
-      <c r="G1" t="str">
-        <v>Giá bán</v>
-      </c>
-      <c r="H1" t="str">
-        <v>Giá khuyến mãi</v>
-      </c>
-      <c r="I1" t="str">
-        <v>Số lượng nhập</v>
-      </c>
-      <c r="J1" t="str">
-        <v>Loài mục tiêu</v>
-      </c>
-      <c r="K1" t="str">
-        <v>Thông số kỹ thuật</v>
-      </c>
-      <c r="L1" t="str">
-        <v>Mô tả</v>
+    <row r="1" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>128222</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Luoc chai long tu dong cho thu cung</v>
-      </c>
-      <c r="C2" t="str">
-        <v>GROOMING</v>
-      </c>
-      <c r="D2" t="str">
-        <v>FurCare</v>
-      </c>
-      <c r="E2" t="str">
-        <v>cái</v>
-      </c>
-      <c r="F2">
+    <row r="2" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2">
         <v>60000</v>
       </c>
-      <c r="G2">
+      <c r="H2">
         <v>135000</v>
       </c>
-      <c r="H2">
+      <c r="I2">
         <v>109000</v>
       </c>
-      <c r="I2">
+      <c r="J2">
         <v>10</v>
       </c>
-      <c r="J2" t="str">
-        <v>ALL</v>
-      </c>
-      <c r="K2" t="str">
-        <v>Màu sắc: Hồng, Kích thước: Trung bình, Chất liệu: Nhựa &amp; Thép</v>
-      </c>
-      <c r="L2" t="str">
-        <v>Lược chải lông tự động cho chó mèo.</v>
+      <c r="K2" t="s">
+        <v>19</v>
+      </c>
+      <c r="L2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M2" t="s">
+        <v>21</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>999999</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Sản phẩm thử nghiệm mới Excel</v>
-      </c>
-      <c r="C3" t="str">
-        <v>ACCESSORY</v>
-      </c>
-      <c r="D3" t="str">
-        <v>PetBrand</v>
-      </c>
-      <c r="E3" t="str">
-        <v>cái</v>
-      </c>
-      <c r="F3">
+    <row r="3" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3">
+        <v>55000</v>
+      </c>
+      <c r="H3">
+        <v>120000</v>
+      </c>
+      <c r="I3">
+        <v>99000</v>
+      </c>
+      <c r="J3">
+        <v>15</v>
+      </c>
+      <c r="K3" t="s">
+        <v>19</v>
+      </c>
+      <c r="L3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G4">
         <v>50000</v>
       </c>
-      <c r="G3">
+      <c r="H4">
         <v>100000</v>
       </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3">
+      <c r="I4" t="s">
+        <v>29</v>
+      </c>
+      <c r="J4">
         <v>20</v>
       </c>
-      <c r="J3" t="str">
-        <v>CAT</v>
-      </c>
-      <c r="K3" t="str">
-        <v>Chất liệu: Cotton, Độ bền: Cao</v>
-      </c>
-      <c r="L3" t="str">
-        <v>Sản phẩm test tạo mới hoàn toàn từ file Excel.</v>
+      <c r="K4" t="s">
+        <v>30</v>
+      </c>
+      <c r="L4" t="s">
+        <v>31</v>
+      </c>
+      <c r="M4" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L3"/>
+    <ignoredError sqref="A2:M4 B1:M1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>